--- a/Configs/GameConfig/Datas/item.xlsx
+++ b/Configs/GameConfig/Datas/item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f7a4498b7dc4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4c72157bda684657"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -889,38 +889,18 @@
       <x:c r="B1" s="3" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>desc</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>price</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>upgrade_to_item_id</x:v>
-      </x:c>
-      <x:c r="G1" s="3" t="str">
-        <x:v>expire_time</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="str">
-        <x:v>batch_useable</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="str">
-        <x:v>quality</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="str">
-        <x:v>exchange_stream</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="str">
-        <x:v>exchange_list</x:v>
-      </x:c>
-      <x:c r="L1" s="7" t="str">
-        <x:v>exchange_column</x:v>
-      </x:c>
-      <x:c r="M1" s="8"/>
-      <x:c r="N1" s="9"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
+      <x:c r="M1"/>
+      <x:c r="N1"/>
       <x:c r="O1"/>
       <x:c r="P1"/>
       <x:c r="Q1"/>
@@ -945,25 +925,23 @@
     </x:row>
     <x:row r="2" s="1" customFormat="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B2" s="3"/>
-      <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
-      <x:c r="E2" s="3"/>
-      <x:c r="F2" s="3"/>
-      <x:c r="G2" s="3"/>
-      <x:c r="H2" s="3"/>
-      <x:c r="I2" s="3"/>
-      <x:c r="J2" s="3"/>
-      <x:c r="K2" s="3"/>
-      <x:c r="L2" s="7" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="M2" s="10" t="str">
-        <x:v>num</x:v>
-      </x:c>
-      <x:c r="N2" s="9"/>
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
       <x:c r="O2"/>
       <x:c r="P2"/>
       <x:c r="Q2"/>
@@ -988,43 +966,21 @@
     </x:row>
     <x:row r="3" s="2" customFormat="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D3" s="4" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="str">
-        <x:v>int#ref=item.TbItem</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="str">
-        <x:v>datetime?</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="str">
-        <x:v>item.EQuality</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str">
-        <x:v>item.ItemExchange</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="str">
-        <x:v>(list#sep=;),item.ItemExchange</x:v>
-      </x:c>
-      <x:c r="L3" s="12" t="str">
-        <x:v>item.ItemExchange</x:v>
-      </x:c>
-      <x:c r="M3" s="13"/>
-      <x:c r="N3" s="9"/>
+        <x:v>##group</x:v>
+      </x:c>
+      <x:c r="B3" s="4"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
       <x:c r="O3"/>
       <x:c r="P3"/>
       <x:c r="Q3"/>
@@ -1049,31 +1005,23 @@
     </x:row>
     <x:row r="4" s="2" customFormat="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>##group</x:v>
-      </x:c>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="E4" s="4"/>
-      <x:c r="F4" s="4"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="str">
-        <x:v>s</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="K4" s="4" t="str">
-        <x:v>c,s</x:v>
-      </x:c>
-      <x:c r="L4" s="12"/>
-      <x:c r="M4" s="13"/>
-      <x:c r="N4" s="9"/>
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
       <x:c r="O4"/>
       <x:c r="P4"/>
       <x:c r="Q4"/>
@@ -1097,42 +1045,22 @@
       <x:c r="AI4"/>
     </x:row>
     <x:row r="5" s="1" customFormat="1">
-      <x:c r="A5" s="3" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
-        <x:v>这是id</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>名字</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>描述</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="str">
-        <x:v>价格</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="str">
-        <x:v>引用当前表</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="str">
-        <x:v>过期时间</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="str">
-        <x:v>能否批量使用</x:v>
-      </x:c>
-      <x:c r="I5" s="3" t="str">
-        <x:v>品质</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="str">
-        <x:v>道具兑换配置</x:v>
-      </x:c>
-      <x:c r="K5" s="3"/>
-      <x:c r="L5" s="10" t="str">
-        <x:v>道具兑换配置</x:v>
-      </x:c>
-      <x:c r="M5" s="3"/>
-      <x:c r="N5" s="9"/>
+      <x:c r="A5" s="3"/>
+      <x:c r="B5" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
       <x:c r="O5"/>
       <x:c r="P5"/>
       <x:c r="Q5"/>
@@ -1158,41 +1086,19 @@
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>发型</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>初始发型</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H6" s="15" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="5" t="str">
-        <x:v>WHITE</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>2,2</x:v>
-      </x:c>
-      <x:c r="K6" s="5" t="str">
-        <x:v>2,2;3,3</x:v>
-      </x:c>
-      <x:c r="L6" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M6" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
+      <x:c r="M6"/>
       <x:c r="N6"/>
       <x:c r="O6"/>
       <x:c r="P6"/>
@@ -1219,41 +1125,19 @@
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>外套</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>初始外套</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G7" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="str">
-        <x:v>WHITE</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>3,2</x:v>
-      </x:c>
-      <x:c r="K7" s="5" t="str">
-        <x:v>2,2;3,4</x:v>
-      </x:c>
-      <x:c r="L7" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M7" s="14" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
+      <x:c r="M7"/>
       <x:c r="N7"/>
       <x:c r="O7"/>
       <x:c r="P7"/>
@@ -1280,41 +1164,19 @@
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>上衣</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>初始上衣</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G8" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="5" t="str">
-        <x:v>BLUE</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>4,3</x:v>
-      </x:c>
-      <x:c r="K8" s="5" t="str">
-        <x:v>2,2;3,5</x:v>
-      </x:c>
-      <x:c r="L8" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M8" s="14" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
+      <x:c r="M8"/>
       <x:c r="N8"/>
       <x:c r="O8"/>
       <x:c r="P8"/>
@@ -1341,41 +1203,19 @@
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>裙子</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>初始下装</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G9" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str">
-        <x:v>BLUE</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>5,3</x:v>
-      </x:c>
-      <x:c r="K9" s="5" t="str">
-        <x:v>2,2;3,6</x:v>
-      </x:c>
-      <x:c r="L9" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M9" s="14" t="n">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+      <x:c r="M9"/>
       <x:c r="N9"/>
       <x:c r="O9"/>
       <x:c r="P9"/>
@@ -1402,41 +1242,19 @@
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>袜子</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>初始袜子</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G10" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H10" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str">
-        <x:v>BLUE</x:v>
-      </x:c>
-      <x:c r="J10" t="str">
-        <x:v>6,4</x:v>
-      </x:c>
-      <x:c r="K10" s="5" t="str">
-        <x:v>2,2;3,7</x:v>
-      </x:c>
-      <x:c r="L10" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="n">
-        <x:v>6</x:v>
-      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10"/>
       <x:c r="N10"/>
       <x:c r="O10"/>
       <x:c r="P10"/>
@@ -1463,41 +1281,19 @@
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>鞋子</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>初始鞋子</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G11" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str">
-        <x:v>PURPLE</x:v>
-      </x:c>
-      <x:c r="J11" t="str">
-        <x:v>7,4</x:v>
-      </x:c>
-      <x:c r="K11" s="5" t="str">
-        <x:v>2,2;3,8</x:v>
-      </x:c>
-      <x:c r="L11" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="n">
-        <x:v>7</x:v>
-      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11"/>
       <x:c r="N11"/>
       <x:c r="O11"/>
       <x:c r="P11"/>
@@ -1524,41 +1320,19 @@
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>发饰</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>初始发饰</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G12" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>N</x:v>
-      </x:c>
-      <x:c r="I12" s="5" t="str">
-        <x:v>PURPLE</x:v>
-      </x:c>
-      <x:c r="J12" t="str">
-        <x:v>8,5</x:v>
-      </x:c>
-      <x:c r="K12" s="5" t="str">
-        <x:v>2,2;3,9</x:v>
-      </x:c>
-      <x:c r="L12" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="n">
-        <x:v>8</x:v>
-      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
+      <x:c r="M12"/>
       <x:c r="N12"/>
       <x:c r="O12"/>
       <x:c r="P12"/>
@@ -1585,41 +1359,19 @@
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="5" t="str">
-        <x:v>中秋节发饰</x:v>
-      </x:c>
-      <x:c r="D13" s="5" t="str">
-        <x:v>中秋节发饰</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G13" s="6" t="n">
-        <x:v>44479.9999884259</x:v>
-      </x:c>
-      <x:c r="H13" s="15" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="5" t="str">
-        <x:v>BLUE</x:v>
-      </x:c>
-      <x:c r="J13" t="str">
-        <x:v>9,5</x:v>
-      </x:c>
-      <x:c r="K13" s="5" t="str">
-        <x:v>2,2;3,10</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="n">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
+      <x:c r="M13"/>
       <x:c r="N13"/>
       <x:c r="O13"/>
       <x:c r="P13"/>
@@ -1646,41 +1398,19 @@
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="5" t="str">
-        <x:v>中秋节鞋子</x:v>
-      </x:c>
-      <x:c r="D14" s="5" t="str">
-        <x:v>中秋节鞋子</x:v>
-      </x:c>
-      <x:c r="E14" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="F14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G14" s="6" t="n">
-        <x:v>44480.9999884259</x:v>
-      </x:c>
-      <x:c r="H14" s="15" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="5" t="str">
-        <x:v>PURPLE</x:v>
-      </x:c>
-      <x:c r="J14" t="str">
-        <x:v>10,6</x:v>
-      </x:c>
-      <x:c r="K14" s="5" t="str">
-        <x:v>2,2;3,11</x:v>
-      </x:c>
-      <x:c r="L14" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
+      <x:c r="M14"/>
       <x:c r="N14"/>
       <x:c r="O14"/>
       <x:c r="P14"/>
@@ -1706,42 +1436,18 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
-      <x:c r="B15" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="5" t="str">
-        <x:v>礼包</x:v>
-      </x:c>
-      <x:c r="D15" s="5" t="str">
-        <x:v>中秋节礼包</x:v>
-      </x:c>
-      <x:c r="E15" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="F15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" s="5" t="str">
-        <x:v>null</x:v>
-      </x:c>
-      <x:c r="H15" s="15" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I15" s="5" t="str">
-        <x:v>RED</x:v>
-      </x:c>
-      <x:c r="J15" t="str">
-        <x:v>1,6</x:v>
-      </x:c>
-      <x:c r="K15" s="5" t="str">
-        <x:v>2,2;3,12</x:v>
-      </x:c>
-      <x:c r="L15" s="14" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="n">
-        <x:v>11</x:v>
-      </x:c>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
+      <x:c r="M15"/>
       <x:c r="N15"/>
       <x:c r="O15"/>
       <x:c r="P15"/>
